--- a/results/Int Task Remove ACC -0.8/Rando_9_permute.xlsx
+++ b/results/Int Task Remove ACC -0.8/Rando_9_permute.xlsx
@@ -440,97 +440,97 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6428131020547899</v>
+        <v>0.6234181272613766</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6404830870852325</v>
+        <v>0.635869711147957</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6475756701058609</v>
+        <v>0.6302730769488953</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6475756701058609</v>
+        <v>0.6483165960703233</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6668869026441743</v>
+        <v>0.6504648618168881</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6719057320650605</v>
+        <v>0.6640953822607388</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6692169176137317</v>
+        <v>0.6758340661479905</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6670313957937557</v>
+        <v>0.6558705166846794</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6679587699454248</v>
+        <v>0.6545657150145332</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6647619638985293</v>
+        <v>0.6700882398351335</v>
       </c>
     </row>
     <row r="12">
@@ -540,787 +540,787 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6697482362102183</v>
+        <v>0.6679866280904081</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6756664138176399</v>
+        <v>0.6791428082352704</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6783785552698884</v>
+        <v>0.6708201035114688</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6888963475622445</v>
+        <v>0.6778568024219804</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6879689734105754</v>
+        <v>0.6745156710456538</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6879689734105754</v>
+        <v>0.6742547107116246</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6689146735226792</v>
+        <v>0.6751215017889628</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6615099450221187</v>
+        <v>0.6726795507790211</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6634392054722795</v>
+        <v>0.6740449355234981</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6626143694325666</v>
+        <v>0.6970468688116319</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.672815149460626</v>
+        <v>0.6899403567185118</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6790738341534144</v>
+        <v>0.6919114043861474</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6843210667991326</v>
+        <v>0.6936961716867267</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6843210667991326</v>
+        <v>0.7046192496425431</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6821308460149427</v>
+        <v>0.7174996140136538</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.658686538810088</v>
+        <v>0.7174996140136538</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.643811799770422</v>
+        <v>0.7130585893709429</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6456571501453323</v>
+        <v>0.7112691231061496</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6491894286730796</v>
+        <v>0.7401521457484443</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6580620800300734</v>
+        <v>0.7460097402815351</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6735987017433157</v>
+        <v>0.7416016083883223</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6900113446421738</v>
+        <v>0.7239776396431472</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6583373050768951</v>
+        <v>0.7186931509240178</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6635657418657573</v>
+        <v>0.7207435775228404</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6638267021997866</v>
+        <v>0.705966845451067</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6603969617839953</v>
+        <v>0.7083341164940357</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6462817767454974</v>
+        <v>0.7212611348669857</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6429775658022809</v>
+        <v>0.7285399982546704</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6409737932052977</v>
+        <v>0.7266107378045097</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6536818062818439</v>
+        <v>0.7104311970946975</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6622562412313971</v>
+        <v>0.7075467043478845</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.656953124475562</v>
+        <v>0.7057666360115191</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6723172270740893</v>
+        <v>0.7024766897810955</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6551542602823406</v>
+        <v>0.7054125354939618</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6614171404788916</v>
+        <v>0.7167363679691747</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6453822607388114</v>
+        <v>0.7110977787324879</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5694615993931623</v>
+        <v>0.7101937315817385</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5874774281897576</v>
+        <v>0.7134230947378314</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6002178305553505</v>
+        <v>0.7084089642811591</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5882603091918452</v>
+        <v>0.6984318885137176</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5906881633091449</v>
+        <v>0.6984318885137176</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5632687001993704</v>
+        <v>0.6984318885137176</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5334447099732159</v>
+        <v>0.6766186253515832</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.536557605944861</v>
+        <v>0.6871362498237888</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5352108492370896</v>
+        <v>0.6748152300142982</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.534661070424048</v>
+        <v>0.6426612248185865</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5346796984607536</v>
+        <v>0.6421299062220999</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5346796984607536</v>
+        <v>0.6433368687445039</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5028286086366962</v>
+        <v>0.6433554967812095</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.502567648302667</v>
+        <v>0.612236102813337</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5021063107089394</v>
+        <v>0.5937591042431647</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5000186280367056</v>
+        <v>0.6007305211151313</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4998182507770073</v>
+        <v>0.6007305211151313</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5000792111110366</v>
+        <v>0.5990249649255885</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5003401714450658</v>
+        <v>0.5926221227235197</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5005405487047641</v>
+        <v>0.5991414321100363</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4993569131832797</v>
+        <v>0.6036989239371949</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5</v>
+        <v>0.6042814276795844</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5</v>
+        <v>0.6017696634870342</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5007828810020877</v>
+        <v>0.6017696634870342</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5013048016701461</v>
+        <v>0.629454450254751</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5010438413361169</v>
+        <v>0.6583091112916111</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5010438413361169</v>
+        <v>0.6583091112916111</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5006617148534259</v>
+        <v>0.5744945257066907</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4999394169256691</v>
+        <v>0.5744292436681457</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5</v>
+        <v>0.5739818351469098</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5</v>
+        <v>0.6031301814471467</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5</v>
+        <v>0.5875470735522156</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5</v>
+        <v>0.5854827178809014</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5</v>
+        <v>0.581120904349227</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4992963301089489</v>
+        <v>0.5754031040015036</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4992963301089489</v>
+        <v>0.5630678194792205</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5</v>
+        <v>0.5659291530452645</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4988536205519269</v>
+        <v>0.5133972504346542</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4990539978116252</v>
+        <v>0.5026278957366969</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4996784565916399</v>
+        <v>0.502567312662366</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4999394169256691</v>
+        <v>0.5118034624653451</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4999394169256691</v>
+        <v>0.5219716853842075</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4999394169256691</v>
+        <v>0.4990352019547691</v>
       </c>
     </row>
   </sheetData>
